--- a/branches/dev/StructureDefinition-mii-pr-seltene-geburtslaenge.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-geburtslaenge.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T14:10:38+00:00</t>
+    <t>2026-09-14T07:31:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-geburtslaenge.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-geburtslaenge.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:31:58+00:00</t>
+    <t>2026-09-14T08:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-geburtslaenge.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-geburtslaenge.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:42:11+00:00</t>
+    <t>2026-09-14T10:17:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-geburtslaenge.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-geburtslaenge.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T10:17:04+00:00</t>
+    <t>2026-09-14T14:24:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-geburtslaenge.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-geburtslaenge.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T14:24:38+00:00</t>
+    <t>2026-09-14T17:50:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-geburtslaenge.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-geburtslaenge.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T17:50:54+00:00</t>
+    <t>2026-09-14T18:57:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-geburtslaenge.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-geburtslaenge.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T18:57:54+00:00</t>
+    <t>2026-09-14T20:28:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-geburtslaenge.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-geburtslaenge.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T20:28:04+00:00</t>
+    <t>2026-09-14T21:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
